--- a/artfynd/A 34334-2025 artfynd.xlsx
+++ b/artfynd/A 34334-2025 artfynd.xlsx
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 34334-2025 artfynd.xlsx
+++ b/artfynd/A 34334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>81412089</v>
       </c>
       <c r="B2" t="n">
-        <v>109389</v>
+        <v>109399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
